--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_rf_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_rf_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.564103658296977</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1040,27 +1041,27 @@
         <v>0.837551214756322</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
@@ -1068,7 +1069,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1076,15 +1077,15 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1189,51 +1190,51 @@
         <v>0.9362579517153848</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1342,51 +1343,51 @@
         <v>0.8375512147563215</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="n">
@@ -1394,7 +1395,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AR6" s="3" t="n">
@@ -1402,15 +1403,15 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -1509,51 +1510,51 @@
         <v>1.162427856303454</v>
       </c>
       <c r="AD7" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AF7" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH7" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1662,59 +1663,59 @@
         <v>1.017052787592159</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR8" s="3" t="n">
@@ -1722,15 +1723,15 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1829,11 +1830,11 @@
         <v>0.3492118895236964</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
@@ -1841,23 +1842,23 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1865,15 +1866,15 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1982,35 +1983,35 @@
         <v>1.004280911438253</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
@@ -2018,23 +2019,23 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR10" s="3" t="n">
@@ -2042,15 +2043,15 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -2349,66 +2350,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.0903200482301444</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.04076898034342899</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582909292</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493482</v>
+        <v>0.2044255219913533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2456,34 +2459,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>38944</v>
+        <v>36119</v>
       </c>
       <c r="M3" t="n">
-        <v>1607</v>
+        <v>89</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.3754608976947175</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="P3" t="n">
-        <v>1572</v>
+        <v>87</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.1513752318139535</v>
+        <v>0.1106615069328753</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.1393683562842672</v>
+        <v>0.05080470069205879</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2493,29 +2496,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3754608976947175</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>969</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.601180768840295</v>
+        <v>0.2436869610882062</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2571,34 +2576,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="M4" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P4" t="n">
-        <v>829</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1481278166620073</v>
+        <v>0.08381851803583454</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.1055945425444167</v>
+        <v>0.03605284870827317</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2608,38 +2613,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4347647734522189</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03377381373985046</v>
+        <v>-0.01475185198378562</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.07243925854050137</v>
+        <v>0.0400918497515339</v>
       </c>
       <c r="AH4" t="n">
-        <v>-589</v>
+        <v>-11</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2694,34 +2701,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36669</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>36766</v>
+        <v>36476</v>
       </c>
       <c r="M5" t="n">
-        <v>109</v>
+        <v>335</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.09240561973392902</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1219414188912732</v>
+        <v>-0.1996068404243396</v>
       </c>
       <c r="P5" t="n">
-        <v>98</v>
+        <v>333</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.06528652259681934</v>
+        <v>0.1240894709636694</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.01572121887894577</v>
+        <v>0.1100754917254131</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2731,38 +2738,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-596</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.09240561973392902</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1219414188912732</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>67</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>304</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>249</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1018137856988925</v>
+        <v>0.2436869610882062</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1236471374053214</v>
+        <v>0.05927079103335435</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2830552779607884</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-902</v>
+        <v>246</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2821,34 +2830,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>38947</v>
+        <v>36119</v>
       </c>
       <c r="M6" t="n">
-        <v>1610</v>
+        <v>89</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3428483979105338</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3642340500887142</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="P6" t="n">
-        <v>1586</v>
+        <v>87</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.147260479271011</v>
+        <v>0.1055140596392438</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1357063951904175</v>
+        <v>0.0484415075065573</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2858,50 +2867,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3428483979105338</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3642340500887142</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1027</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5217188801190165</v>
+        <v>0.2436869610882062</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.003661961093849725</v>
+        <v>-0.002363193185501496</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.03261249978418368</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.03011185264600073</v>
+        <v>0.01238865879828412</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.03982675875631769</v>
+        <v>-0.0400918497515339</v>
       </c>
       <c r="AL6" t="n">
-        <v>647</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -2952,76 +2963,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37691</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36166</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>119</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.5172771893471498</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.537556826654351</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="P7" t="n">
-        <v>1851</v>
+        <v>117</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.323969150388525</v>
+        <v>0.1141311677770472</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.323969150388525</v>
+        <v>0.06050356242010013</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.1613052792804081</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>742</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.5172771893471498</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.537556826654351</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1154</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>33</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.071582237117751</v>
+        <v>0.2436869610882062</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.1846007941042578</v>
+        <v>0.009698861728041332</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.1418162916524324</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>30</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -3077,34 +3092,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>39192</v>
+        <v>36119</v>
       </c>
       <c r="M8" t="n">
-        <v>1777</v>
+        <v>89</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4335107453073743</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4519459771853966</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="P8" t="n">
-        <v>1750</v>
+        <v>87</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2312715351201362</v>
+        <v>0.1057243185549729</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2239001559162285</v>
+        <v>0.04853803738020102</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -3114,50 +3129,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X8" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4335107453073743</v>
+        <v>-0.1959391460331658</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4519459771853966</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1194</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.7652585494187267</v>
+        <v>0.2436869610882062</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.08453179963196134</v>
+        <v>-0.002266663311857771</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-0.05804984761265686</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.1183056133718118</v>
+        <v>0.01248518867192785</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.1304891061531582</v>
+        <v>-0.0400918497515339</v>
       </c>
       <c r="AL8" t="n">
-        <v>814</v>
+        <v>11</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -3208,75 +3225,73 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>36811</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>36987</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.09001351452255157</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1158160953193689</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.03408491929112597</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.01269131077129871</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-497</v>
+        <v>-31</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.09001351452255157</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1158160953193689</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>121</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.09891741905960671</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1266770455129685</v>
+        <v>-0.05080470069205879</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2854473831721659</v>
+        <v>0.1959391460331658</v>
       </c>
       <c r="AH9" t="n">
-        <v>-848</v>
+        <v>-58</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3286,10 +3301,10 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>0.04878377108627574</v>
+        <v>0.09933463918678509</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.03905676935899827</v>
+        <v>-0.08094202744966106</v>
       </c>
     </row>
     <row r="10">
@@ -3339,34 +3354,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>38958</v>
+        <v>36104</v>
       </c>
       <c r="M10" t="n">
-        <v>1617</v>
+        <v>78</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.3716982741005919</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.3907546470334907</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P10" t="n">
-        <v>1558</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.1532647893144445</v>
+        <v>0.08381851803583454</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.1415461253967673</v>
+        <v>0.03605284870827317</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -3376,59 +3391,61 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3716982741005919</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3907546470334907</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1034</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.5915919991601315</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.002177769112500144</v>
+        <v>-0.01475185198378562</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.003762623594125603</v>
+        <v>0.0400918497515339</v>
       </c>
       <c r="AH10" t="n">
-        <v>65</v>
+        <v>-11</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.0359515828523506</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.06867663494637577</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.04878377108627574</v>
+        <v>0.09933463918678509</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>-0.04773491163227539</v>
+        <v>-0.01680582695486188</v>
       </c>
     </row>
   </sheetData>
@@ -3726,68 +3743,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.503509252857314</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2352416489517779</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1561727120528913</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459927</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616547</v>
+        <v>0.9463998245842122</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3835,34 +3850,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>38944</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1606</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.375472295585537</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3957852429007653</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1572</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1514223231922318</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1394051046979009</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39877</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>41477</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1455</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.6100001664268992</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.6100001664268992</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1454</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2848395462178516</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.2069212638990652</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3872,31 +3887,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>353</v>
+        <v>637</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.375472295585537</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.3957852429007653</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1102</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>242</v>
-      </c>
+        <v>969</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.564103658296978</v>
+        <v>0.6012099910564699</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3952,34 +3965,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38012</v>
+      </c>
+      <c r="M4" t="n">
+        <v>962</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.3013243461981798</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.343246110573307</v>
+      </c>
+      <c r="P4" t="n">
+        <v>813</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1482043849238123</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1056221565201652</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40911</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1067</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1066</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1974000942251041</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1228166173480004</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3989,40 +4002,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3013243461981798</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>712</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-148</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.8375512147563215</v>
+        <v>0.4312792989973724</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.08410464655106478</v>
+        <v>-0.03378294817773571</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1542026855020535</v>
+        <v>0.07414794938735714</v>
       </c>
       <c r="AH4" t="n">
-        <v>-390</v>
+        <v>-589</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4077,34 +4088,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>36669</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>36766</v>
+      </c>
+      <c r="M5" t="n">
+        <v>108</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.09242218340723074</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1219414188912731</v>
+      </c>
+      <c r="P5" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.06558531831164577</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.01572536422348158</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>40763</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>41127</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1216</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.1357141689401175</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.1788222766520315</v>
-      </c>
-      <c r="P5" t="n">
-        <v>282</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.05307386043653663</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.03524926915774564</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4114,40 +4125,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>965</v>
+        <v>41</v>
       </c>
       <c r="X5" t="n">
-        <v>610</v>
+        <v>-596</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1357141689401175</v>
+        <v>-0.09242218340723074</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1788222766520315</v>
+        <v>-0.1219414188912731</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>251</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-609</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1570246370621278</v>
+        <v>0.1018338942595605</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1716719947413196</v>
+        <v>-0.1236797404744193</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.4742859974867818</v>
+        <v>0.2830501121783062</v>
       </c>
       <c r="AH5" t="n">
-        <v>-851</v>
+        <v>-902</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4156,12 +4165,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1158795430432833</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.08262100919868676</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4210,34 +4215,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>38947</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1609</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3428603909822003</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3642340500887141</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1586</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.147306205239904</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1357421780243129</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40981</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1115</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1114</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1966389564323735</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1250621261669873</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -4247,62 +4252,56 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3428603909822003</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3642340500887141</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>760</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-100</v>
-      </c>
+        <v>1027</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.8375512147563215</v>
+        <v>0.5217466521226137</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.08185913773207784</v>
+        <v>-0.003662926673588029</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1542026855020535</v>
+        <v>0.03261190460333663</v>
       </c>
       <c r="AH6" t="n">
-        <v>-342</v>
+        <v>58</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.002245508818986941</v>
+        <v>0.03012002150414768</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.04153604478402051</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>647</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1158795430432833</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>0.00492481533305944</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4347,80 +4346,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37691</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.517285999078793</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.5375568266543511</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1851</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.3240545740288729</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.3240545740288729</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>40004</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40588</v>
-      </c>
-      <c r="M7" t="n">
-        <v>844</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3389624169517775</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3389624169517775</v>
-      </c>
-      <c r="P7" t="n">
-        <v>843</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1921489179640864</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1063384798044704</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.1613205855291641</v>
+      </c>
       <c r="W7" t="n">
-        <v>441</v>
+        <v>741</v>
       </c>
       <c r="X7" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3389624169517775</v>
+        <v>-0.517285999078793</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3389624169517775</v>
+        <v>-0.5375568266543511</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>403</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-457</v>
-      </c>
+        <v>1154</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.5127732910264049</v>
+        <v>1.071620044356719</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.1005827840945948</v>
+        <v>0.184649469330972</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2710377494751217</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-699</v>
-      </c>
+        <v>-0.1418137034932561</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4476,34 +4471,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>39192</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1776</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.4335210837836228</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.4519459771853965</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1750</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.2313365995566802</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.2239591935325257</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>41158</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1238</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.5042271545140171</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.5042271545140171</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1237</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.2347179175069832</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1572917869134339</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -4513,52 +4508,50 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.5042271545140171</v>
+        <v>-0.4335210837836228</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.5042271545140171</v>
+        <v>-0.4519459771853965</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>883</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>23</v>
-      </c>
+        <v>1194</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1.017052787592162</v>
+        <v>0.765290766122761</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.0496294769856313</v>
+        <v>0.08455408883462481</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1057730119128821</v>
+        <v>-0.05804878819808579</v>
       </c>
       <c r="AH8" t="n">
-        <v>-219</v>
+        <v>225</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.03447516956543348</v>
+        <v>0.1183370370123605</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.04842967358917138</v>
+        <v>-0.1321967375854429</v>
       </c>
       <c r="AL8" t="n">
-        <v>171</v>
+        <v>814</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -4609,34 +4602,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>36811</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>36990</v>
+      </c>
+      <c r="M9" t="n">
+        <v>262</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.09022032350692788</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1158160953193688</v>
+      </c>
+      <c r="P9" t="n">
+        <v>172</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.03412890418773015</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.01271103901979829</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>40420</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>41338</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1359</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2588265729313863</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2588265729313863</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1358</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1547364451561194</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.1086391150538242</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4646,40 +4639,38 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>728</v>
+        <v>140</v>
       </c>
       <c r="X9" t="n">
-        <v>373</v>
+        <v>-497</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2588265729313863</v>
+        <v>-0.09022032350692788</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2588265729313863</v>
+        <v>-0.1158160953193688</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>631</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-229</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.3492118895236993</v>
+        <v>0.0991672223924589</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.09828214884524102</v>
+        <v>-0.1266940656781027</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3511735934955129</v>
+        <v>0.2852519720786091</v>
       </c>
       <c r="AH9" t="n">
-        <v>-471</v>
+        <v>-847</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4688,8 +4679,12 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.04880291182708141</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.03885587127619017</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4738,34 +4733,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>38958</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1616</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3701682235946616</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3907546470334906</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1548</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1533119886990864</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.1415832771935679</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>41120</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1211</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.5010679419770513</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.5010679419770513</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1210</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2374183865396628</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1573583557415437</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -4775,58 +4770,60 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.5010679419770513</v>
+        <v>-0.3701682235946616</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.5010679419770513</v>
+        <v>-0.3907546470334906</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>856</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-4</v>
-      </c>
+        <v>1034</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>1.004280911438255</v>
+        <v>0.5877255442831673</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.04956290815752146</v>
+        <v>0.002178172495666986</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.108932224449848</v>
+        <v>0.005304071990875348</v>
       </c>
       <c r="AH10" t="n">
-        <v>-246</v>
+        <v>65</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.03454173839354333</v>
+        <v>0.03596112067340269</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.04527046105220556</v>
+        <v>-0.06884387739648179</v>
       </c>
       <c r="AL10" t="n">
-        <v>144</v>
+        <v>654</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="n">
+        <v>0.04880291182708141</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.05006558616960655</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5123,34 +5120,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856417</v>
+        <v>0.2352416489517779</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.0521896337568788</v>
+        <v>0.1562010221613542</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5160,22 +5157,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5184,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160741</v>
+        <v>1.014136226616547</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5232,34 +5229,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39877</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43537</v>
+        <v>41477</v>
       </c>
       <c r="M3" t="n">
-        <v>117</v>
+        <v>1455</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="P3" t="n">
-        <v>115</v>
+        <v>1454</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.06178239628542021</v>
+        <v>0.2848395462178516</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.03567008312656749</v>
+        <v>0.2069587734187967</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5269,31 +5266,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>353</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>53</v>
+        <v>1102</v>
       </c>
       <c r="AC3" t="n">
-        <v>-23</v>
+        <v>242</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2130666245979118</v>
+        <v>1.564103658296978</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -5349,34 +5346,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43545</v>
+        <v>40911</v>
       </c>
       <c r="M4" t="n">
-        <v>123</v>
+        <v>1067</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="P4" t="n">
-        <v>119</v>
+        <v>1066</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.1974000942251041</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02899795472484739</v>
+        <v>0.1228388808517359</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -5386,40 +5383,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>59</v>
+        <v>712</v>
       </c>
       <c r="AC4" t="n">
-        <v>-17</v>
+        <v>-148</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.8375512147563215</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.006672128401720098</v>
+        <v>-0.08411989256706078</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03306617978599624</v>
+        <v>0.1542026855020535</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>-390</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5474,34 +5471,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>40763</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43537</v>
+        <v>41127</v>
       </c>
       <c r="M5" t="n">
-        <v>117</v>
+        <v>1216</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.1357141689401175</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.1788222766520315</v>
       </c>
       <c r="P5" t="n">
-        <v>115</v>
+        <v>282</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.06178239628542021</v>
+        <v>0.05307386043653663</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.03567008312656749</v>
+        <v>0.03525565894646081</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5511,40 +5508,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>965</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.1357141689401175</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.1788222766520315</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>53</v>
+        <v>251</v>
       </c>
       <c r="AC5" t="n">
-        <v>-23</v>
+        <v>-609</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2130666245979118</v>
+        <v>0.1570246370621278</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1717031144723359</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>0.4742859974867818</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-851</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5553,8 +5550,12 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1158795430432833</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.08262100919868676</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5603,34 +5604,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43537</v>
+        <v>40981</v>
       </c>
       <c r="M6" t="n">
-        <v>117</v>
+        <v>1115</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="P6" t="n">
-        <v>115</v>
+        <v>1114</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.06178239628542021</v>
+        <v>0.1966389564323735</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.03567008312656749</v>
+        <v>0.1250847967238974</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5640,58 +5641,62 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>53</v>
+        <v>760</v>
       </c>
       <c r="AC6" t="n">
-        <v>-23</v>
+        <v>-100</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2130666245979118</v>
+        <v>0.8375512147563215</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>-0.08187397669489929</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.1542026855020535</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-342</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.006672128401720098</v>
+        <v>0.002245915872161483</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.03306617978599624</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-6</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.1158795430432833</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.00492481533305944</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5736,34 +5741,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43700</v>
+        <v>40004</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43787</v>
+        <v>40588</v>
       </c>
       <c r="M7" t="n">
-        <v>291</v>
+        <v>844</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1071333290755291</v>
+        <v>-0.3389624169517775</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.136961373853965</v>
+        <v>-0.3389624169517775</v>
       </c>
       <c r="P7" t="n">
-        <v>261</v>
+        <v>843</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.06601192624462937</v>
+        <v>0.1921489179640864</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05995317680301169</v>
+        <v>0.1063577562443649</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5773,40 +5778,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>231</v>
+        <v>441</v>
       </c>
       <c r="X7" t="n">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1071333290755291</v>
+        <v>-0.3389624169517775</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.136961373853965</v>
+        <v>-0.3389624169517775</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>60</v>
+        <v>403</v>
       </c>
       <c r="AC7" t="n">
-        <v>-16</v>
+        <v>-457</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1199880481198874</v>
+        <v>0.5127732910264049</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.0242830936764442</v>
+        <v>-0.1006010171744318</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.06850964079723931</v>
+        <v>0.2710377494751217</v>
       </c>
       <c r="AH7" t="n">
-        <v>7</v>
+        <v>-699</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5865,34 +5870,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43559</v>
+        <v>41158</v>
       </c>
       <c r="M8" t="n">
-        <v>133</v>
+        <v>1238</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1530640146787772</v>
+        <v>-0.5042271545140171</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1532653413160446</v>
+        <v>-0.5042271545140171</v>
       </c>
       <c r="P8" t="n">
-        <v>131</v>
+        <v>1237</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.05421982007341408</v>
+        <v>0.2347179175069832</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.03335867868757021</v>
+        <v>0.1573202998814762</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5902,52 +5907,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1530640146787772</v>
+        <v>-0.5042271545140171</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1532653413160446</v>
+        <v>-0.5042271545140171</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>69</v>
+        <v>883</v>
       </c>
       <c r="AC8" t="n">
-        <v>-7</v>
+        <v>23</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.180726781399805</v>
+        <v>1.017052787592162</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.002311404438997279</v>
+        <v>-0.04963847353732048</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02257895519399122</v>
+        <v>0.1057730119128821</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>-219</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.004360723962722819</v>
+        <v>0.03448141902974029</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.01048722459200502</v>
+        <v>-0.04842967358917138</v>
       </c>
       <c r="AL8" t="n">
-        <v>10</v>
+        <v>171</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -5998,34 +6003,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43700</v>
+        <v>40420</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43768</v>
+        <v>41338</v>
       </c>
       <c r="M9" t="n">
-        <v>278</v>
+        <v>1359</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.07924422852071844</v>
+        <v>-0.2588265729313863</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1369613738539652</v>
+        <v>-0.2588265729313863</v>
       </c>
       <c r="P9" t="n">
-        <v>214</v>
+        <v>1358</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.06632378833801512</v>
+        <v>0.1547364451561194</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05888027033188868</v>
+        <v>0.1086588085399016</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6035,40 +6040,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>231</v>
+        <v>728</v>
       </c>
       <c r="X9" t="n">
-        <v>167</v>
+        <v>373</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.07924422852071844</v>
+        <v>-0.2588265729313863</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1369613738539652</v>
+        <v>-0.2588265729313863</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>47</v>
+        <v>631</v>
       </c>
       <c r="AC9" t="n">
-        <v>-29</v>
+        <v>-229</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.08606432995082414</v>
+        <v>0.3492118895236993</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.02321018720532119</v>
+        <v>-0.09829996487889507</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.09639874135204995</v>
+        <v>0.3511735934955129</v>
       </c>
       <c r="AH9" t="n">
-        <v>-6</v>
+        <v>-471</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6127,34 +6132,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>43537</v>
+        <v>41120</v>
       </c>
       <c r="M10" t="n">
-        <v>117</v>
+        <v>1211</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.1530640146787772</v>
+        <v>-0.5010679419770513</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.1532653413160446</v>
+        <v>-0.5010679419770513</v>
       </c>
       <c r="P10" t="n">
-        <v>115</v>
+        <v>1210</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.05634854628050435</v>
+        <v>0.2374183865396628</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.03253284836349327</v>
+        <v>0.1573868807768078</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -6164,52 +6169,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1530640146787772</v>
+        <v>-0.5010679419770513</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1532653413160446</v>
+        <v>-0.5010679419770513</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>53</v>
+        <v>856</v>
       </c>
       <c r="AC10" t="n">
-        <v>-23</v>
+        <v>-4</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.180726781399805</v>
+        <v>1.004280911438255</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.003137234763074224</v>
+        <v>-0.04957189264198891</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.02257895519399122</v>
+        <v>0.108932224449848</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-246</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.003534893638645873</v>
+        <v>0.03454799992507186</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01048722459200502</v>
+        <v>-0.04527046105220556</v>
       </c>
       <c r="AL10" t="n">
-        <v>-6</v>
+        <v>144</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -6512,34 +6517,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606706</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860074</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428352</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049091</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -6549,22 +6554,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -6573,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986547</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6621,34 +6626,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M3" t="n">
+        <v>118</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1783446632793302</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1783446632793302</v>
+      </c>
+      <c r="P3" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.06381830295717236</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.03694915879991898</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44076</v>
-      </c>
-      <c r="M3" t="n">
-        <v>137</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.341225014720676</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.341225014720676</v>
-      </c>
-      <c r="P3" t="n">
-        <v>136</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1443875768739651</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.07790766720830088</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -6658,31 +6663,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="AC3" t="n">
-        <v>59</v>
+        <v>-25</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.5179689914546388</v>
+        <v>0.2170553215063706</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6738,34 +6743,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43545</v>
+      </c>
+      <c r="M4" t="n">
+        <v>124</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1419538085967058</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1452798889626854</v>
+      </c>
+      <c r="P4" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04879934490473427</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.02895708373240715</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44061</v>
-      </c>
-      <c r="M4" t="n">
-        <v>126</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="P4" t="n">
-        <v>125</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1183626651723915</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.0612671142774218</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6775,40 +6780,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="AC4" t="n">
-        <v>48</v>
+        <v>-19</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.1654384228016292</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01664055293087908</v>
+        <v>-0.007992075067511831</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.04527439408206202</v>
+        <v>0.03639085468262437</v>
       </c>
       <c r="AH4" t="n">
-        <v>-11</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6863,76 +6868,80 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M5" t="n">
+        <v>118</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1783446632793302</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1783446632793302</v>
+      </c>
+      <c r="P5" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.06381830295717236</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.03694915879991898</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>473</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.341225014720676</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.341225014720676</v>
-      </c>
-      <c r="P5" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.2729577758300793</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.2729577758300793</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2763935416930963</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-25</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.5179689914546388</v>
+        <v>0.2170553215063706</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.1950501086217784</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -6988,34 +6997,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M6" t="n">
+        <v>118</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1783446632793302</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1783446632793302</v>
+      </c>
+      <c r="P6" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06381830295717236</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.03694915879991898</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44167</v>
-      </c>
-      <c r="M6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.341225014720676</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.341225014720676</v>
-      </c>
-      <c r="P6" t="n">
-        <v>199</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1366476304653278</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.08898380307353367</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7025,52 +7034,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="AC6" t="n">
-        <v>122</v>
+        <v>-25</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5179689914546388</v>
+        <v>0.2170553215063706</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.01107613586523279</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.02771668879611187</v>
+        <v>0.007992075067511831</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.04527439408206202</v>
+        <v>-0.03639085468262437</v>
       </c>
       <c r="AL6" t="n">
-        <v>74</v>
+        <v>-6</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -7121,34 +7130,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43700</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43794</v>
+      </c>
+      <c r="M7" t="n">
+        <v>297</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.11005955146415</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1369613738539651</v>
+      </c>
+      <c r="P7" t="n">
+        <v>270</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.06610248698661295</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.06056361009791996</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44132</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44182</v>
-      </c>
-      <c r="M7" t="n">
-        <v>211</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.03626828091862433</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.1073219548172964</v>
-      </c>
-      <c r="P7" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.05500102006262528</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.03678319959333082</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7158,40 +7167,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="X7" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.03626828091862433</v>
+        <v>-0.11005955146415</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1073219548172964</v>
+        <v>-0.1369613738539651</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AC7" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.03763317134896749</v>
+        <v>0.1236706923988256</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.04112446761497005</v>
+        <v>0.02361445129800098</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.3049567338020517</v>
+        <v>0.06828511181518016</v>
       </c>
       <c r="AH7" t="n">
-        <v>-79</v>
+        <v>12</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7200,12 +7209,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.03001018564506341</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.02853447743218596</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7254,34 +7259,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M8" t="n">
+        <v>134</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1558397068651701</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1558397068651701</v>
+      </c>
+      <c r="P8" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05639140380990274</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.03477487789968355</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M8" t="n">
-        <v>122</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="P8" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1198665936154176</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.06106066763512775</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7291,62 +7296,58 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AC8" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.18460914133553</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.01684699957317313</v>
+        <v>-0.002174280900235435</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.04527439408206202</v>
+        <v>0.02250495641416006</v>
       </c>
       <c r="AH8" t="n">
-        <v>-15</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-0.0002064466422940503</v>
+        <v>0.005817794167276395</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0</v>
+        <v>-0.01388589826846431</v>
       </c>
       <c r="AL8" t="n">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.03001018564506341</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.009449106185097977</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7391,76 +7392,80 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43700</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43770</v>
+      </c>
+      <c r="M9" t="n">
+        <v>281</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.08226185280964493</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1369613738539651</v>
+      </c>
+      <c r="P9" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.0667173109352926</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05946328684176164</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>43889</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>473</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1393867712832274</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.1393867712832274</v>
-      </c>
-      <c r="P9" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.07080509963935513</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.07080509963935513</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.09243017983726198</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>232</v>
       </c>
       <c r="X9" t="n">
-        <v>-16</v>
+        <v>167</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1393867712832274</v>
+        <v>-0.08226185280964493</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1393867712832274</v>
+        <v>-0.1369613738539651</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>466</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-29</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1619621528372992</v>
+        <v>0.08963542930136303</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.007102567568945742</v>
+        <v>0.02251412804184266</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2018382434374486</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.09608281046968525</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-4</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7516,34 +7521,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>43542</v>
+      </c>
+      <c r="M10" t="n">
+        <v>121</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1558397068651701</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1558397068651701</v>
+      </c>
+      <c r="P10" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.05777363909469971</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.03386846103024619</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44070</v>
-      </c>
-      <c r="M10" t="n">
-        <v>133</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3140368405715118</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3140368405715118</v>
-      </c>
-      <c r="P10" t="n">
-        <v>132</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.133911340797722</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.07120009724826017</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -7553,52 +7558,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3140368405715118</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3140368405715118</v>
+        <v>-0.1558397068651701</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="AC10" t="n">
-        <v>55</v>
+        <v>-22</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.457804236649024</v>
+        <v>0.18460914133553</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.00670756996004071</v>
+        <v>-0.003080697769672791</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.02718817414916419</v>
+        <v>0.02250495641416006</v>
       </c>
       <c r="AH10" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.009932982970838368</v>
+        <v>0.00491137729783904</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01808621993289783</v>
+        <v>-0.01388589826846431</v>
       </c>
       <c r="AL10" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -7901,34 +7906,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7938,22 +7943,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7962,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088524</v>
+        <v>0.4088864968986547</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8010,34 +8015,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="M3" t="n">
+        <v>137</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="P3" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1443875768739651</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.07790766720830088</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="M3" t="n">
-        <v>364</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3381261530483139</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3381261530483139</v>
-      </c>
-      <c r="P3" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2115738387606444</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1442691821265061</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8047,31 +8052,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="AC3" t="n">
-        <v>-53</v>
+        <v>59</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.5108619332907343</v>
+        <v>0.5179689914546388</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8127,34 +8132,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44061</v>
+      </c>
+      <c r="M4" t="n">
+        <v>126</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="P4" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1183626651723915</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.0612671142774218</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45135</v>
-      </c>
-      <c r="M4" t="n">
-        <v>393</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2377598766809245</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2377598766809245</v>
-      </c>
-      <c r="P4" t="n">
-        <v>392</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1318162553441144</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09338610296468229</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -8164,40 +8169,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="AC4" t="n">
-        <v>-22</v>
+        <v>48</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3119225417387239</v>
+        <v>0.4203549201436105</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.05088307916182382</v>
+        <v>-0.01664055293087908</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1003662763673895</v>
+        <v>0.04527439408206202</v>
       </c>
       <c r="AH4" t="n">
-        <v>31</v>
+        <v>-11</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8252,91 +8257,83 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>473</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="P5" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2729577758300793</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.2729577758300793</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45315</v>
-      </c>
-      <c r="M5" t="n">
-        <v>516</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.28626934324289</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2944964900151588</v>
-      </c>
-      <c r="P5" t="n">
-        <v>492</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1751390927718808</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1421325470885146</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>-0.2763935416930963</v>
+      </c>
       <c r="W5" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.28626934324289</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2944964900151588</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>319</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>99</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4010887588093479</v>
+        <v>0.5179689914546388</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.002136635037991524</v>
+        <v>0.1950501086217784</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.05185680980542395</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>152</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.7987676932469374</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.4433148926414667</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8385,34 +8382,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44167</v>
+      </c>
+      <c r="M6" t="n">
+        <v>200</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="P6" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1366476304653278</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.08898380307353367</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45279</v>
-      </c>
-      <c r="M6" t="n">
-        <v>493</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3176543999139079</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3176543999139079</v>
-      </c>
-      <c r="P6" t="n">
-        <v>492</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1817812074102761</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1442041071155684</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -8422,62 +8419,58 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3176543999139079</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3176543999139079</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>296</v>
+        <v>177</v>
       </c>
       <c r="AC6" t="n">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4655330083081493</v>
+        <v>0.5179689914546388</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-6.507501093772072e-05</v>
+        <v>0.01107613586523279</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02047175313440608</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.0508180041508861</v>
+        <v>0.02771668879611187</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.07989452323298341</v>
+        <v>-0.04527439408206202</v>
       </c>
       <c r="AL6" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.7987676932469374</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.07008181681004189</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8522,34 +8515,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44132</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44182</v>
+      </c>
+      <c r="M7" t="n">
+        <v>211</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.03626828091862433</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1073219548172964</v>
+      </c>
+      <c r="P7" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.05500102006262528</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.03678319959333082</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44588</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45014</v>
-      </c>
-      <c r="M7" t="n">
-        <v>310</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.135724924640571</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.135724924640571</v>
-      </c>
-      <c r="P7" t="n">
-        <v>309</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.06530913313950705</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04110733151736916</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8559,40 +8552,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>17</v>
+        <v>176</v>
       </c>
       <c r="X7" t="n">
-        <v>-178</v>
+        <v>153</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.135724924640571</v>
+        <v>-0.03626828091862433</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.135724924640571</v>
+        <v>-0.1073219548172964</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>293</v>
+        <v>35</v>
       </c>
       <c r="AC7" t="n">
-        <v>73</v>
+        <v>-20</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1570390359621634</v>
+        <v>0.03763317134896749</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.1031618506091369</v>
+        <v>-0.04112446761497005</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.202401228407743</v>
+        <v>0.3049567338020517</v>
       </c>
       <c r="AH7" t="n">
-        <v>126</v>
+        <v>-79</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8602,10 +8595,10 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" s="3" t="n">
-        <v>0.05993249576779425</v>
+        <v>0.03001018564506341</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.05743937134481081</v>
+        <v>-0.02853447743218596</v>
       </c>
     </row>
     <row r="8">
@@ -8655,34 +8648,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M8" t="n">
+        <v>122</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="P8" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1198665936154176</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.06106066763512775</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45076</v>
-      </c>
-      <c r="M8" t="n">
-        <v>352</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.2613688299955147</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.2613688299955147</v>
-      </c>
-      <c r="P8" t="n">
-        <v>351</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1566140895661365</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1050227423770579</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -8692,61 +8685,61 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2613688299955147</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2613688299955147</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="AC8" t="n">
-        <v>-63</v>
+        <v>44</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3538556733178855</v>
+        <v>0.4203549201436105</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.03924643974944823</v>
+        <v>-0.01684699957317313</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.07675732305279925</v>
+        <v>0.04527439408206202</v>
       </c>
       <c r="AH8" t="n">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.01163663941237558</v>
+        <v>-0.0002064466422940503</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.02360895331459023</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-41</v>
+        <v>-4</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.05993249576779425</v>
+        <v>0.03001018564506341</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.002825702403289609</v>
+        <v>-0.009449106185097977</v>
       </c>
     </row>
     <row r="9">
@@ -8792,91 +8785,83 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43889</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>473</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1393867712832274</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1393867712832274</v>
+      </c>
+      <c r="P9" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.07080509963935513</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.07080509963935513</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45001</v>
-      </c>
-      <c r="M9" t="n">
-        <v>301</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.05022508458098629</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.1076918456382937</v>
-      </c>
-      <c r="P9" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.06290330047813525</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.03901594013189497</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.09243017983726198</v>
+      </c>
       <c r="W9" t="n">
-        <v>297</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>102</v>
+        <v>-16</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.05022508458098629</v>
+        <v>-0.1393867712832274</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1076918456382937</v>
+        <v>-0.1393867712832274</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-216</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.0528810392500505</v>
+        <v>0.1619621528372992</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1052532419946111</v>
+        <v>-0.007102567568945742</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2879010684673277</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-163</v>
-      </c>
+        <v>0.2018382434374486</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.05993249576779425</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.05649586949159147</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8925,34 +8910,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>44070</v>
+      </c>
+      <c r="M10" t="n">
+        <v>133</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3140368405715118</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3140368405715118</v>
+      </c>
+      <c r="P10" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.133911340797722</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.07120009724826017</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45071</v>
-      </c>
-      <c r="M10" t="n">
-        <v>350</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2481399708595511</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2481399708595511</v>
-      </c>
-      <c r="P10" t="n">
-        <v>349</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1377116559854615</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09208511410497136</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -8962,62 +8947,58 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.2481399708595511</v>
+        <v>-0.3140368405715118</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.2481399708595511</v>
+        <v>-0.3140368405715118</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="AC10" t="n">
-        <v>-65</v>
+        <v>55</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.3300347953637499</v>
+        <v>0.457804236649024</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.05218406802153475</v>
+        <v>-0.00670756996004071</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.08998618218876286</v>
+        <v>0.02718817414916419</v>
       </c>
       <c r="AH10" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-0.00130098885971093</v>
+        <v>0.009932982970838368</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01038009417862662</v>
+        <v>-0.01808621993289783</v>
       </c>
       <c r="AL10" t="n">
-        <v>-43</v>
+        <v>7</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.05993249576779425</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>0.003234618606485551</v>
-      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9314,34 +9295,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138081</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138081</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645823</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451878</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -9351,22 +9332,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -9375,7 +9356,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367029</v>
+        <v>0.4792042812088524</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -9423,34 +9404,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="M3" t="n">
+        <v>364</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="P3" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2115738387606444</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1442691821265061</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45832</v>
-      </c>
-      <c r="M3" t="n">
-        <v>86</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1965679708822623</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1965679708822623</v>
-      </c>
-      <c r="P3" t="n">
-        <v>85</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.09334112666390186</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.05896637339200361</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -9460,31 +9441,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>52</v>
+        <v>167</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3</v>
+        <v>-53</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2446603617459924</v>
+        <v>0.5108619332907343</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -9540,34 +9521,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45135</v>
+      </c>
+      <c r="M4" t="n">
+        <v>393</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="P4" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1318162553441144</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09338610296468229</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M4" t="n">
-        <v>136</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="P4" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.06216000016109517</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.04927686199609638</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -9577,40 +9558,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="AC4" t="n">
-        <v>47</v>
+        <v>-22</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1783604398064753</v>
+        <v>0.3119225417387239</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.009689511395907235</v>
+        <v>-0.05088307916182382</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.04520474297572474</v>
+        <v>0.1003662763673895</v>
       </c>
       <c r="AH4" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9665,73 +9646,77 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45315</v>
+      </c>
+      <c r="M5" t="n">
+        <v>516</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.28626934324289</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2944964900151588</v>
+      </c>
+      <c r="P5" t="n">
+        <v>492</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1751390927718808</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1421325470885146</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>88</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.28626934324289</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2944964900151588</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>99</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.4010887588093479</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.05896637339200361</v>
+        <v>-0.002136635037991524</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1965679708822623</v>
+        <v>0.05185680980542395</v>
       </c>
       <c r="AH5" t="n">
-        <v>-52</v>
+        <v>152</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9741,10 +9726,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.1958359094029314</v>
+        <v>0.7987676932469374</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1468927565683013</v>
+        <v>-0.4433148926414667</v>
       </c>
     </row>
     <row r="6">
@@ -9794,34 +9779,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45279</v>
+      </c>
+      <c r="M6" t="n">
+        <v>493</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3176543999139079</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3176543999139079</v>
+      </c>
+      <c r="P6" t="n">
+        <v>492</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1817812074102761</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1442041071155684</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M6" t="n">
-        <v>136</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="P6" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06216000016109517</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.04927686199609638</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -9831,61 +9816,61 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3176543999139079</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3176543999139079</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>296</v>
       </c>
       <c r="AC6" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1783604398064753</v>
+        <v>0.4655330083081493</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.009689511395907235</v>
+        <v>-6.507501093772072e-05</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.04520474297572474</v>
+        <v>0.02047175313440608</v>
       </c>
       <c r="AH6" t="n">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0</v>
+        <v>0.0508180041508861</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.07989452323298341</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1958359094029314</v>
+        <v>0.7987676932469374</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.06234305370981008</v>
+        <v>-0.07008181681004189</v>
       </c>
     </row>
     <row r="7">
@@ -9931,34 +9916,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44588</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45014</v>
+      </c>
+      <c r="M7" t="n">
+        <v>310</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.135724924640571</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.135724924640571</v>
+      </c>
+      <c r="P7" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.06530913313950705</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.04110733151736916</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>45715</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45790</v>
-      </c>
-      <c r="M7" t="n">
-        <v>58</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.05508953650041504</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.05508953650041504</v>
-      </c>
-      <c r="P7" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.04706421982058542</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.02448435246916725</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -9968,40 +9953,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="X7" t="n">
-        <v>-28</v>
+        <v>-178</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.05508953650041504</v>
+        <v>-0.135724924640571</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.05508953650041504</v>
+        <v>-0.135724924640571</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>52</v>
+        <v>293</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3</v>
+        <v>73</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.05830132973275015</v>
+        <v>0.1570390359621634</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.03448202092283636</v>
+        <v>-0.1031618506091369</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1414784343818473</v>
+        <v>0.202401228407743</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -10010,8 +9995,12 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.05993249576779425</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.05743937134481081</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10060,34 +10049,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45076</v>
+      </c>
+      <c r="M8" t="n">
+        <v>352</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.2613688299955147</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.2613688299955147</v>
+      </c>
+      <c r="P8" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1566140895661365</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.1050227423770579</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45820</v>
-      </c>
-      <c r="M8" t="n">
-        <v>79</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1717607303038212</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1717607303038212</v>
-      </c>
-      <c r="P8" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.0861804442252902</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.05220660778195112</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -10097,58 +10086,62 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1717607303038212</v>
+        <v>-0.2613688299955147</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1717607303038212</v>
+        <v>-0.2613688299955147</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="AC8" t="n">
+        <v>-63</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.3538556733178855</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.03924643974944823</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.07675732305279925</v>
+      </c>
+      <c r="AH8" t="n">
         <v>-10</v>
       </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="3" t="n">
-        <v>0.2073805681380307</v>
-      </c>
-      <c r="AF8" s="3" t="n">
-        <v>-0.006759765610052496</v>
-      </c>
-      <c r="AG8" s="3" t="n">
-        <v>0.02480724057844108</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-7</v>
-      </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.00292974578585474</v>
+        <v>0.01163663941237558</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.02039750239728366</v>
+        <v>-0.02360895331459023</v>
       </c>
       <c r="AL8" t="n">
-        <v>-57</v>
+        <v>-41</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.05993249576779425</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.002825702403289609</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10193,34 +10186,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>301</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.05022508458098629</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1076918456382937</v>
+      </c>
+      <c r="P9" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.06290330047813525</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.03901594013189497</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>45729</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45887</v>
-      </c>
-      <c r="M9" t="n">
-        <v>124</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1256532754890514</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.1256532754890514</v>
-      </c>
-      <c r="P9" t="n">
-        <v>123</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.08672790748101199</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.06567281432453202</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -10230,40 +10223,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>16</v>
+        <v>297</v>
       </c>
       <c r="X9" t="n">
-        <v>-18</v>
+        <v>102</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1256532754890514</v>
+        <v>-0.05022508458098629</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1256532754890514</v>
+        <v>-0.1076918456382937</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>108</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>53</v>
+        <v>-216</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1437110381574696</v>
+        <v>0.0528810392500505</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.00670644093252841</v>
+        <v>-0.1052532419946111</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.07091469539321094</v>
+        <v>0.2879010684673277</v>
       </c>
       <c r="AH9" t="n">
-        <v>56</v>
+        <v>-163</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10272,8 +10265,12 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.05993249576779425</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.05649586949159147</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10322,34 +10319,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45071</v>
+      </c>
+      <c r="M10" t="n">
+        <v>350</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.2481399708595511</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.2481399708595511</v>
+      </c>
+      <c r="P10" t="n">
+        <v>349</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1377116559854615</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.09208511410497136</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45883</v>
-      </c>
-      <c r="M10" t="n">
-        <v>122</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.189144434109547</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.189144434109547</v>
-      </c>
-      <c r="P10" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.09225423473986763</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.0692963914351976</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -10359,58 +10356,62 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.189144434109547</v>
+        <v>-0.2481399708595511</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.189144434109547</v>
+        <v>-0.2481399708595511</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AC10" t="n">
-        <v>33</v>
+        <v>-65</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.2332652596419378</v>
+        <v>0.3300347953637499</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.01033001804319399</v>
+        <v>-0.05218406802153475</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.007423536772715345</v>
+        <v>0.08998618218876286</v>
       </c>
       <c r="AH10" t="n">
-        <v>36</v>
+        <v>-12</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.02001952943910122</v>
+        <v>-0.00130098885971093</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.0377812062030094</v>
+        <v>-0.01038009417862662</v>
       </c>
       <c r="AL10" t="n">
-        <v>-14</v>
+        <v>-43</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="n">
+        <v>0.05993249576779425</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>0.003234618606485551</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10423,7 +10424,1400 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451878</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367029</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45832</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="P3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.09334112666390186</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05896637339200361</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>52</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2446603617459924</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M4" t="n">
+        <v>136</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="P4" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.06216000016109517</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.04927686199609638</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.1783604398064753</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.009689511395907235</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.04520474297572474</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.05896637339200361</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.1965679708822623</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1958359094029314</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.1468927565683013</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M6" t="n">
+        <v>136</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="P6" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06216000016109517</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.04927686199609638</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1783604398064753</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.009689511395907235</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.04520474297572474</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>0.1958359094029314</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.06234305370981008</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>45715</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45790</v>
+      </c>
+      <c r="M7" t="n">
+        <v>58</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.05508953650041504</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.05508953650041504</v>
+      </c>
+      <c r="P7" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.04706421982058542</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.02448435246916725</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-28</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.05508953650041504</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.05508953650041504</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>52</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.05830132973275015</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.03448202092283636</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.1414784343818473</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45820</v>
+      </c>
+      <c r="M8" t="n">
+        <v>79</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1717607303038212</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1717607303038212</v>
+      </c>
+      <c r="P8" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.0861804442252902</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.05220660778195112</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1717607303038212</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1717607303038212</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.2073805681380307</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.006759765610052496</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.02480724057844108</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>0.00292974578585474</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>-0.02039750239728366</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-57</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>45729</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="M9" t="n">
+        <v>124</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1256532754890514</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1256532754890514</v>
+      </c>
+      <c r="P9" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.08672790748101199</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06567281432453202</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>-0.1256532754890514</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-0.1256532754890514</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>108</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>53</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0.1437110381574696</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>0.00670644093252841</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.07091469539321094</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>56</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="M10" t="n">
+        <v>122</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.189144434109547</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.189144434109547</v>
+      </c>
+      <c r="P10" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.09225423473986763</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.0692963914351976</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.189144434109547</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.189144434109547</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>88</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.2332652596419378</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>0.01033001804319399</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.007423536772715345</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>0.02001952943910122</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>-0.0377812062030094</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10529,24 +11923,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -10577,20 +11969,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -10623,20 +12015,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -10672,16 +12068,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -10711,24 +12105,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -10759,21 +12151,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -10790,37 +12184,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -10847,27 +12239,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -10894,14 +12284,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -10911,10 +12301,10 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -10941,27 +12331,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -10988,27 +12378,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -11035,27 +12425,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -11072,37 +12462,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -11119,24 +12509,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -11146,10 +12536,10 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -11176,27 +12566,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -11223,27 +12613,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -11270,27 +12660,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -11317,14 +12707,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -11334,7 +12724,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" s="3" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -11343,6 +12733,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
